--- a/backend/assets/client-import-template.xlsx
+++ b/backend/assets/client-import-template.xlsx
@@ -1,217 +1,196 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="KPI" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet sheetId="1" name="KPI" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
-  <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
-  <si>
-    <t xml:space="preserve">Наименование</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Юридическое название</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Адрес</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Телефон</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Контактное лицо</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ориентир</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ИНН</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ПИНФЛ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Торговый канал (код)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Категория клиента (код)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Тип клиента (код)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Формат (код)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Город (код)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Широта</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Долгота</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Агент 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Агент 1 день</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Экспедитор 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Агент 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Агент 2 день</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Экспедитор 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Агент 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Агент 3 день</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Экспедитор 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Агент 4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Агент 4 день</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Экспедитор 4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Агент 5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Агент 5 день</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Экспедитор 5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Агент 6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Агент 6 день</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Экспедитор 6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Агент 7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Агент 7 день</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Экспедитор 7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Агент 8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Агент 8 день</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Экспедитор 8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Агент 9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Агент 9 день</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Экспедитор 9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Агент 10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Агент 10 день</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Экспедитор 10</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
+  <si>
+    <t>ИД</t>
+  </si>
+  <si>
+    <t>Наименование</t>
+  </si>
+  <si>
+    <t>Юридическое название</t>
+  </si>
+  <si>
+    <t>Адрес</t>
+  </si>
+  <si>
+    <t>Телефон</t>
+  </si>
+  <si>
+    <t>Контактное лицо</t>
+  </si>
+  <si>
+    <t>Ориентир</t>
+  </si>
+  <si>
+    <t>ИНН</t>
+  </si>
+  <si>
+    <t>ПИНФЛ</t>
+  </si>
+  <si>
+    <t>Торговый канал (код)</t>
+  </si>
+  <si>
+    <t>Категория клиента (код)</t>
+  </si>
+  <si>
+    <t>Тип клиента (код)</t>
+  </si>
+  <si>
+    <t>Формат (код)</t>
+  </si>
+  <si>
+    <t>Город (код)</t>
+  </si>
+  <si>
+    <t>Широта</t>
+  </si>
+  <si>
+    <t>Долгота</t>
+  </si>
+  <si>
+    <t>Агент 1</t>
+  </si>
+  <si>
+    <t>Агент 1 день</t>
+  </si>
+  <si>
+    <t>Экспедитор 1</t>
+  </si>
+  <si>
+    <t>Агент 2</t>
+  </si>
+  <si>
+    <t>Агент 2 день</t>
+  </si>
+  <si>
+    <t>Экспедитор 2</t>
+  </si>
+  <si>
+    <t>Агент 3</t>
+  </si>
+  <si>
+    <t>Агент 3 день</t>
+  </si>
+  <si>
+    <t>Экспедитор 3</t>
+  </si>
+  <si>
+    <t>Агент 4</t>
+  </si>
+  <si>
+    <t>Агент 4 день</t>
+  </si>
+  <si>
+    <t>Экспедитор 4</t>
+  </si>
+  <si>
+    <t>Агент 5</t>
+  </si>
+  <si>
+    <t>Агент 5 день</t>
+  </si>
+  <si>
+    <t>Экспедитор 5</t>
+  </si>
+  <si>
+    <t>Агент 6</t>
+  </si>
+  <si>
+    <t>Агент 6 день</t>
+  </si>
+  <si>
+    <t>Экспедитор 6</t>
+  </si>
+  <si>
+    <t>Агент 7</t>
+  </si>
+  <si>
+    <t>Агент 7 день</t>
+  </si>
+  <si>
+    <t>Экспедитор 7</t>
+  </si>
+  <si>
+    <t>Агент 8</t>
+  </si>
+  <si>
+    <t>Агент 8 день</t>
+  </si>
+  <si>
+    <t>Экспедитор 8</t>
+  </si>
+  <si>
+    <t>Агент 9</t>
+  </si>
+  <si>
+    <t>Агент 9 день</t>
+  </si>
+  <si>
+    <t>Экспедитор 9</t>
+  </si>
+  <si>
+    <t>Агент 10</t>
+  </si>
+  <si>
+    <t>Агент 10 день</t>
+  </si>
+  <si>
+    <t>Экспедитор 10</t>
+  </si>
+  <si>
+    <t/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
-  <fonts count="7">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
+      <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <charset val="204"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
       <charset val="204"/>
+      <color theme="1"/>
+      <family val="2"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="204"/>
+      <b/>
+      <charset val="1"/>
+      <color rgb="FF000000"/>
+      <family val="2"/>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="204"/>
-    </font>
-    <font>
+      <b/>
+      <charset val="1"/>
+      <color theme="1"/>
+      <family val="2"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -229,14 +208,14 @@
     </fill>
   </fills>
   <borders count="2">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left style="thin"/>
       <right style="thin"/>
       <top style="thin"/>
@@ -244,121 +223,37 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FFA6A6A6"/>
-      <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF333333"/>
-    </indexedColors>
-  </colors>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -535,18 +430,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:AS1"/>
-  <sheetFormatPr defaultColWidth="8.89453125" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:AT2"/>
+  <sheetFormatPr defaultRowHeight="14.25" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.89453125" customHeight="1"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="45" min="1" style="1" width="14.66"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="46" style="1" width="8.89"/>
+    <col min="1" max="45" width="14.66" style="1" customWidth="1"/>
+    <col min="46" max="16384" width="8.89" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="26.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" ht="26.5" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -682,14 +574,62 @@
       <c r="AS1" s="4" t="s">
         <v>44</v>
       </c>
+      <c r="AT1" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+      <c r="V2" s="1"/>
+      <c r="W2" s="1"/>
+      <c r="X2" s="1"/>
+      <c r="Y2" s="1"/>
+      <c r="Z2" s="1"/>
+      <c r="AA2" s="1"/>
+      <c r="AB2" s="1"/>
+      <c r="AC2" s="1"/>
+      <c r="AD2" s="1"/>
+      <c r="AE2" s="1"/>
+      <c r="AF2" s="1"/>
+      <c r="AG2" s="1"/>
+      <c r="AH2" s="1"/>
+      <c r="AI2" s="1"/>
+      <c r="AJ2" s="1"/>
+      <c r="AK2" s="1"/>
+      <c r="AL2" s="1"/>
+      <c r="AM2" s="1"/>
+      <c r="AN2" s="1"/>
+      <c r="AO2" s="1"/>
+      <c r="AP2" s="1"/>
+      <c r="AQ2" s="1"/>
+      <c r="AR2" s="1"/>
+      <c r="AS2" s="1"/>
+      <c r="AT2" s="1"/>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>